--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 129 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 124 clubs short</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="P38" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="10" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5103,8 +5103,8 @@
       <c r="Y43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="10" t="n">
-        <v>0</v>
+      <c r="Z43" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="9" t="n">
         <v>1</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X57" s="9" t="n">
         <v>7</v>
@@ -7705,17 +7705,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="10" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8247,8 +8247,8 @@
       <c r="P74" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" s="10" t="n">
-        <v>0</v>
+      <c r="Q74" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R74" s="10" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10726,8 +10726,8 @@
       <c r="Y98" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="10" t="n">
-        <v>0</v>
+      <c r="Z98" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="9" t="n">
         <v>1</v>
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16427,8 +16427,8 @@
       <c r="T154" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U154" s="10" t="n">
-        <v>0</v>
+      <c r="U154" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V154" s="10" t="n">
         <v>0</v>
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17365,8 +17365,8 @@
       <c r="Y163" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="10" t="n">
-        <v>0</v>
+      <c r="Z163" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="9" t="n">
         <v>1</v>
@@ -18834,7 +18834,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18904,8 +18904,8 @@
       <c r="Y178" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="10" t="n">
-        <v>0</v>
+      <c r="Z178" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA178" s="9" t="n">
         <v>1</v>
@@ -19343,7 +19343,7 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19413,8 +19413,8 @@
       <c r="Y183" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z183" s="10" t="n">
-        <v>0</v>
+      <c r="Z183" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA183" s="9" t="n">
         <v>1</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F214" s="6" t="n">
         <v>10</v>
@@ -22552,8 +22552,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P214" s="10" t="n">
-        <v>3</v>
+      <c r="P214" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q214" s="9" t="n">
         <v>2</v>
@@ -24132,7 +24132,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -24312,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -24330,7 +24330,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -24495,7 +24495,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -24858,7 +24858,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -24924,7 +24924,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -25023,7 +25023,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -25056,7 +25056,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -25287,7 +25287,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1448,7 +1452,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1751,7 +1759,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1953,7 +1965,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2054,7 +2070,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2462,7 +2482,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2971,7 +2995,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3072,7 +3100,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3274,7 +3306,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3892,7 +3928,11 @@
       <c r="AB31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4094,7 +4134,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4195,7 +4239,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4502,7 +4550,11 @@
       <c r="AB37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4809,7 +4861,11 @@
       <c r="AB40" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5011,7 +5067,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5322,7 +5382,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5625,7 +5689,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6037,7 +6105,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6138,7 +6210,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6441,7 +6517,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6744,7 +6824,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6950,7 +7034,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7463,7 +7551,11 @@
       <c r="AB66" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -8283,7 +8375,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8384,7 +8480,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8485,7 +8585,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8788,7 +8892,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8889,7 +8997,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -8990,7 +9102,11 @@
       <c r="AB81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9091,7 +9207,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9499,7 +9619,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9600,7 +9724,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -10016,7 +10144,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10218,7 +10350,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10529,7 +10665,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10840,7 +10980,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11046,7 +11190,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11252,7 +11400,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11452,7 +11604,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11755,7 +11911,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11961,7 +12121,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12262,7 +12426,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12464,7 +12632,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -13280,7 +13452,11 @@
       <c r="AB123" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13783,7 +13959,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -15122,7 +15302,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15429,7 +15613,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15530,7 +15718,11 @@
       <c r="AB145" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC145" s="4" t="inlineStr"/>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -15631,7 +15823,11 @@
       <c r="AB146" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -16148,7 +16344,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16350,7 +16550,11 @@
       <c r="AB153" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16766,7 +16970,11 @@
       <c r="AB157" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -17071,7 +17279,11 @@
       <c r="AB160" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC160" s="4" t="inlineStr"/>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17479,7 +17691,11 @@
       <c r="AB164" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC164" s="4" t="inlineStr"/>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -17996,7 +18212,11 @@
       <c r="AB169" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC169" s="4" t="inlineStr"/>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -18509,7 +18729,11 @@
       <c r="AB174" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -18812,7 +19036,11 @@
       <c r="AB177" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC177" s="4" t="inlineStr"/>
+      <c r="AC177" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -18913,7 +19141,11 @@
       <c r="AB178" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC178" s="4" t="inlineStr"/>
+      <c r="AC178" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -19014,7 +19246,11 @@
       <c r="AB179" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC179" s="4" t="inlineStr"/>
+      <c r="AC179" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -19834,7 +20070,11 @@
       <c r="AB187" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC187" s="4" t="inlineStr"/>
+      <c r="AC187" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -20036,7 +20276,11 @@
       <c r="AB189" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC189" s="4" t="inlineStr"/>
+      <c r="AC189" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -20137,7 +20381,11 @@
       <c r="AB190" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC190" s="4" t="inlineStr"/>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -20238,7 +20486,11 @@
       <c r="AB191" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC191" s="4" t="inlineStr"/>
+      <c r="AC191" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -20440,7 +20692,11 @@
       <c r="AB193" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -20541,7 +20797,11 @@
       <c r="AB194" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC194" s="4" t="inlineStr"/>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -21268,7 +21528,11 @@
       <c r="AB201" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC201" s="4" t="inlineStr"/>
+      <c r="AC201" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -21468,7 +21732,11 @@
       <c r="AB203" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC203" s="4" t="inlineStr"/>
+      <c r="AC203" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -22082,7 +22350,11 @@
       <c r="AB209" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC209" s="4" t="inlineStr"/>
+      <c r="AC209" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -22183,7 +22455,11 @@
       <c r="AB210" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC210" s="4" t="inlineStr"/>
+      <c r="AC210" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -22591,7 +22867,11 @@
       <c r="AB214" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC214" s="4" t="inlineStr"/>
+      <c r="AC214" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -22692,7 +22972,11 @@
       <c r="AB215" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC215" s="4" t="inlineStr"/>
+      <c r="AC215" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -22894,7 +23178,11 @@
       <c r="AB217" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC217" s="4" t="inlineStr"/>
+      <c r="AC217" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -22995,7 +23283,11 @@
       <c r="AB218" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC218" s="4" t="inlineStr"/>
+      <c r="AC218" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -23302,7 +23594,11 @@
       <c r="AB221" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC221" s="4" t="inlineStr"/>
+      <c r="AC221" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -23403,7 +23699,11 @@
       <c r="AB222" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC222" s="4" t="inlineStr"/>
+      <c r="AC222" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 124 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 105 clubs short</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
       <c r="U3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="10" t="n">
-        <v>0</v>
+      <c r="V3" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="9" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1855,8 +1855,8 @@
       <c r="Y11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="10" t="n">
-        <v>0</v>
+      <c r="Z11" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="9" t="n">
         <v>1</v>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="P22" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="10" t="n">
         <v>1</v>
@@ -2971,8 +2971,8 @@
       <c r="T22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U22" s="10" t="n">
-        <v>0</v>
+      <c r="U22" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
         <v>0</v>
@@ -2986,8 +2986,8 @@
       <c r="Y22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="10" t="n">
-        <v>0</v>
+      <c r="Z22" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="9" t="n">
         <v>1</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="10" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3503,8 +3503,8 @@
       <c r="Y27" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="10" t="n">
-        <v>0</v>
+      <c r="Z27" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="9" t="n">
         <v>1</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4125,8 +4125,8 @@
       <c r="Y33" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="10" t="n">
-        <v>0</v>
+      <c r="Z33" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>1</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>7</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="X49" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y49" s="10" t="n">
         <v>0</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5991,8 +5991,8 @@
       <c r="Y51" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="10" t="n">
-        <v>0</v>
+      <c r="Z51" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="9" t="n">
         <v>1</v>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="P53" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="10" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="P55" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="9" t="n">
         <v>2</v>
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X57" s="9" t="n">
         <v>7</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7336,8 +7336,8 @@
       <c r="Y64" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="10" t="n">
-        <v>0</v>
+      <c r="Z64" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="9" t="n">
         <v>1</v>
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="10" t="n">
         <v>0</v>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11181,8 +11181,8 @@
       <c r="Y101" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="10" t="n">
-        <v>0</v>
+      <c r="Z101" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="9" t="n">
         <v>1</v>
@@ -11674,7 +11674,7 @@
         <v>1</v>
       </c>
       <c r="Q106" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="10" t="n">
         <v>0</v>
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11846,13 +11846,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11872,8 +11872,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P108" s="10" t="n">
-        <v>3</v>
+      <c r="P108" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>0</v>
@@ -11894,7 +11894,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" s="9" t="n">
         <v>7</v>
@@ -11937,7 +11937,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -12007,8 +12007,8 @@
       <c r="Y109" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="10" t="n">
-        <v>0</v>
+      <c r="Z109" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="9" t="n">
         <v>1</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12522,8 +12522,8 @@
       <c r="Y114" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="10" t="n">
-        <v>0</v>
+      <c r="Z114" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="9" t="n">
         <v>1</v>
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="P124" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q124" s="10" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15273,7 +15273,7 @@
         <v>0</v>
       </c>
       <c r="S141" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" s="10" t="n">
         <v>0</v>
@@ -15293,8 +15293,8 @@
       <c r="Y141" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>0</v>
+      <c r="Z141" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="9" t="n">
         <v>1</v>
@@ -15863,13 +15863,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>4</v>
       </c>
       <c r="W147" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X147" s="9" t="n">
         <v>7</v>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16335,8 +16335,8 @@
       <c r="Y151" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="10" t="n">
-        <v>0</v>
+      <c r="Z151" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="9" t="n">
         <v>1</v>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16541,8 +16541,8 @@
       <c r="Y153" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="10" t="n">
-        <v>0</v>
+      <c r="Z153" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="9" t="n">
         <v>1</v>
@@ -16891,7 +16891,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16905,13 +16905,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>1</v>
       </c>
       <c r="V157" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W157" s="10" t="n">
         <v>0</v>
@@ -16961,8 +16961,8 @@
       <c r="Y157" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="10" t="n">
-        <v>0</v>
+      <c r="Z157" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="9" t="n">
         <v>1</v>
@@ -17200,7 +17200,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17249,8 +17249,8 @@
       <c r="R160" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S160" s="10" t="n">
-        <v>0</v>
+      <c r="S160" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T160" s="10" t="n">
         <v>0</v>
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="P163" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q163" s="10" t="n">
         <v>0</v>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17993,8 +17993,8 @@
       <c r="Y167" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="10" t="n">
-        <v>0</v>
+      <c r="Z167" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="9" t="n">
         <v>1</v>
@@ -18384,10 +18384,10 @@
         </is>
       </c>
       <c r="P171" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q171" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="10" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18693,8 +18693,8 @@
       <c r="P174" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="Q174" s="10" t="n">
-        <v>1</v>
+      <c r="Q174" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R174" s="10" t="n">
         <v>0</v>
@@ -18957,7 +18957,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -19027,8 +19027,8 @@
       <c r="Y177" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="10" t="n">
-        <v>0</v>
+      <c r="Z177" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="9" t="n">
         <v>1</v>
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20582,8 +20582,8 @@
       <c r="Y192" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z192" s="10" t="n">
-        <v>0</v>
+      <c r="Z192" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA192" s="9" t="n">
         <v>1</v>
@@ -20613,7 +20613,7 @@
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20683,8 +20683,8 @@
       <c r="Y193" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z193" s="10" t="n">
-        <v>0</v>
+      <c r="Z193" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA193" s="9" t="n">
         <v>1</v>
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -22551,8 +22551,8 @@
       <c r="Y211" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z211" s="10" t="n">
-        <v>0</v>
+      <c r="Z211" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA211" s="9" t="n">
         <v>1</v>
@@ -22596,13 +22596,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>0</v>
       </c>
       <c r="V212" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W212" s="10" t="n">
         <v>0</v>
@@ -22835,7 +22835,7 @@
         <v>2</v>
       </c>
       <c r="R214" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S214" s="10" t="n">
         <v>1</v>
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F218" s="6" t="n">
         <v>10</v>
@@ -23218,13 +23218,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
@@ -23250,8 +23250,8 @@
       <c r="Q218" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R218" s="10" t="n">
-        <v>1</v>
+      <c r="R218" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S218" s="9" t="n">
         <v>2</v>
@@ -23265,8 +23265,8 @@
       <c r="V218" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W218" s="10" t="n">
-        <v>1</v>
+      <c r="W218" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="X218" s="9" t="n">
         <v>7</v>
@@ -23661,7 +23661,7 @@
         </is>
       </c>
       <c r="P222" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q222" s="9" t="n">
         <v>2</v>
@@ -23826,7 +23826,7 @@
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" s="6" t="n">
         <v>10</v>
@@ -23896,8 +23896,8 @@
       <c r="Y224" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z224" s="10" t="n">
-        <v>0</v>
+      <c r="Z224" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA224" s="9" t="n">
         <v>1</v>
@@ -24201,7 +24201,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -24234,7 +24234,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -24300,7 +24300,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -24366,7 +24366,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -24498,7 +24498,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -24564,7 +24564,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -24795,7 +24795,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -24861,7 +24861,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -24894,7 +24894,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -25059,7 +25059,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -25158,7 +25158,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -25191,7 +25191,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -25257,7 +25257,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -25290,13 +25290,13 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25323,7 +25323,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -25422,7 +25422,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -25554,7 +25554,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -25620,7 +25620,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -25653,7 +25653,7 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -12,8 +12,8 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$230</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC230"/>
+  <dimension ref="A1:AC231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="P5" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="10" t="n">
         <v>1</v>
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="10" t="n">
         <v>0</v>
@@ -1898,17 +1898,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2037,8 +2037,8 @@
       <c r="S13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="10" t="n">
-        <v>0</v>
+      <c r="T13" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="10" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2471,8 +2471,8 @@
       <c r="Y17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="10" t="n">
-        <v>0</v>
+      <c r="Z17" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="9" t="n">
         <v>1</v>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="10" t="n">
         <v>0</v>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="10" t="n">
         <v>0</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="10" t="n">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="P28" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="10" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4709,8 +4709,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="10" t="n">
-        <v>3</v>
+      <c r="P39" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5023,8 +5023,8 @@
       <c r="P42" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="10" t="n">
-        <v>1</v>
+      <c r="Q42" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5346,8 +5346,8 @@
       <c r="T45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U45" s="10" t="n">
-        <v>0</v>
+      <c r="U45" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V45" s="10" t="n">
         <v>0</v>
@@ -5410,13 +5410,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="P46" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="10" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="10" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5544,8 +5544,8 @@
       <c r="P47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" s="10" t="n">
-        <v>1</v>
+      <c r="Q47" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>W L 4 Toastmasters Club</t>
+          <t>We Lead Together (W L 4 TMC)</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6177,8 +6177,8 @@
       <c r="U53" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="10" t="n">
-        <v>3</v>
+      <c r="V53" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="10" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6682,8 +6682,8 @@
       <c r="Q58" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R58" s="10" t="n">
-        <v>0</v>
+      <c r="R58" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S58" s="10" t="n">
         <v>0</v>
@@ -6755,13 +6755,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X59" s="9" t="n">
         <v>7</v>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="P61" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>2</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7200,10 +7200,10 @@
         <v>2</v>
       </c>
       <c r="R63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S63" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="S68" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>1</v>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="P69" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>2</v>
@@ -8403,13 +8403,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="10" t="n">
         <v>0</v>
@@ -8718,13 +8718,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8823,13 +8823,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="10" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9054,8 +9054,8 @@
       <c r="P81" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="Q81" s="10" t="n">
-        <v>1</v>
+      <c r="Q81" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R81" s="10" t="n">
         <v>0</v>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9572,8 +9572,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P86" s="10" t="n">
-        <v>1</v>
+      <c r="P86" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q86" s="10" t="n">
         <v>0</v>
@@ -9584,8 +9584,8 @@
       <c r="S86" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="10" t="n">
-        <v>0</v>
+      <c r="T86" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="10" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9901,8 +9901,8 @@
       <c r="U89" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="V89" s="10" t="n">
-        <v>2</v>
+      <c r="V89" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="10" t="n">
         <v>0</v>
@@ -9962,13 +9962,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         </is>
       </c>
       <c r="P90" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="10" t="n">
         <v>0</v>
@@ -10687,13 +10687,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10923,8 +10923,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P99" s="10" t="n">
-        <v>3</v>
+      <c r="P99" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>1</v>
@@ -11527,13 +11527,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X105" s="9" t="n">
         <v>5</v>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12181,8 +12181,8 @@
       <c r="S111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="10" t="n">
-        <v>0</v>
+      <c r="T111" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="10" t="n">
         <v>0</v>
@@ -12190,8 +12190,8 @@
       <c r="V111" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W111" s="10" t="n">
-        <v>3</v>
+      <c r="W111" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>7</v>
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12274,8 +12274,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P112" s="10" t="n">
-        <v>3</v>
+      <c r="P112" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q112" s="10" t="n">
         <v>0</v>
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12496,8 +12496,8 @@
       <c r="S114" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="10" t="n">
-        <v>0</v>
+      <c r="T114" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="10" t="n">
         <v>0</v>
@@ -12587,7 +12587,7 @@
         <v>2</v>
       </c>
       <c r="Q115" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="10" t="n">
         <v>0</v>
@@ -12658,13 +12658,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12943,19 +12943,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28680691</v>
+        <v>832585</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Bread N Wine</t>
+          <t>Accra Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12969,17 +12969,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="P119" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q119" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="10" t="n">
         <v>0</v>
@@ -13013,14 +13013,14 @@
       <c r="U119" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="10" t="n">
-        <v>0</v>
+      <c r="V119" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="10" t="n">
-        <v>0</v>
+      <c r="X119" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="Y119" s="10" t="n">
         <v>0</v>
@@ -13031,8 +13031,14 @@
       <c r="AA119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB119" s="4" t="n"/>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AB119" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13046,15 +13052,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>832585</v>
+        <v>28679118</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Accra Toastmasters Club</t>
+          <t>Garden City Speakers</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13068,25 +13074,25 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L120" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
@@ -13095,10 +13101,10 @@
         </is>
       </c>
       <c r="P120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q120" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="Q120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="R120" s="10" t="n">
         <v>0</v>
@@ -13115,11 +13121,11 @@
       <c r="V120" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W120" s="10" t="n">
-        <v>0</v>
+      <c r="W120" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="X120" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y120" s="10" t="n">
         <v>0</v>
@@ -13127,17 +13133,13 @@
       <c r="Z120" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AA120" s="9" t="n">
-        <v>1</v>
+      <c r="AA120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13151,15 +13153,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28679118</v>
+        <v>6773641</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Garden City Speakers</t>
+          <t>Stanbic Heights Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13173,70 +13175,70 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K121" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M121" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O121" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P121" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W121" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X121" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC121" s="4" t="inlineStr"/>
     </row>
@@ -13252,11 +13254,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>6773641</v>
+        <v>7804114</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Stanbic Heights Toastmasters</t>
+          <t>Stanbic Kumasi L and D Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -13274,25 +13276,25 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
@@ -13301,7 +13303,7 @@
         </is>
       </c>
       <c r="P122" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="10" t="n">
         <v>0</v>
@@ -13319,25 +13321,25 @@
         <v>0</v>
       </c>
       <c r="V122" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W122" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X122" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="Y122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB122" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC122" s="4" t="inlineStr"/>
     </row>
@@ -13353,15 +13355,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>7804114</v>
+        <v>7420582</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Stanbic Kumasi L and D Toastmasters Club</t>
+          <t>Tema Flourish Toastmasters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13375,13 +13377,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-21</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -13389,11 +13391,11 @@
         </is>
       </c>
       <c r="M123" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O123" s="8" t="inlineStr">
@@ -13402,10 +13404,10 @@
         </is>
       </c>
       <c r="P123" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="10" t="n">
         <v>0</v>
@@ -13419,26 +13421,26 @@
       <c r="U123" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="10" t="n">
-        <v>0</v>
+      <c r="V123" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X123" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y123" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="10" t="n">
-        <v>0</v>
+      <c r="Z123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA123" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AC123" s="4" t="inlineStr"/>
     </row>
@@ -13450,19 +13452,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>7420582</v>
+        <v>28680691</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Tema Flourish Toastmasters</t>
+          <t>Bread N Wine</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13476,17 +13478,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -13503,10 +13505,10 @@
         </is>
       </c>
       <c r="P124" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" s="10" t="n">
         <v>0</v>
@@ -13520,14 +13522,14 @@
       <c r="U124" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>4</v>
+      <c r="V124" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="W124" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X124" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X124" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="Y124" s="10" t="n">
         <v>0</v>
@@ -13538,9 +13540,7 @@
       <c r="AA124" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB124" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="AB124" s="4" t="n"/>
       <c r="AC124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
@@ -14317,7 +14317,7 @@
         </is>
       </c>
       <c r="P132" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q132" s="10" t="n">
         <v>0</v>
@@ -14381,7 +14381,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14433,8 +14433,8 @@
       <c r="S133" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="10" t="n">
-        <v>0</v>
+      <c r="T133" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="10" t="n">
         <v>0</v>
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W135" s="10" t="n">
         <v>0</v>
@@ -15221,13 +15221,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17943,8 +17943,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P167" s="10" t="n">
-        <v>3</v>
+      <c r="P167" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q167" s="10" t="n">
         <v>0</v>
@@ -18022,13 +18022,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>4</v>
       </c>
       <c r="W168" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X168" s="9" t="n">
         <v>7</v>
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="P171" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q171" s="10" t="n">
         <v>0</v>
@@ -18543,13 +18543,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L173" s="8" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W173" s="10" t="n">
         <v>0</v>
@@ -19143,15 +19143,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>28678346</v>
+        <v>28681064</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Sanlam Togo Toastmasters Club</t>
+          <t>Nexus Toastmasters Club De Lome</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19165,17 +19165,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L179" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="7" t="n">
@@ -19201,13 +19201,13 @@
         <v>0</v>
       </c>
       <c r="S179" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T179" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T179" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="V179" s="10" t="n">
         <v>0</v>
@@ -19215,8 +19215,8 @@
       <c r="W179" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X179" s="9" t="n">
-        <v>7</v>
+      <c r="X179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="Y179" s="10" t="n">
         <v>0</v>
@@ -19227,9 +19227,7 @@
       <c r="AA179" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB179" s="4" t="n">
-        <v>8</v>
-      </c>
+      <c r="AB179" s="4" t="n"/>
       <c r="AC179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
@@ -19240,19 +19238,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>28679666</v>
+        <v>28678346</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Estrella TMC</t>
+          <t>Sanlam Togo Toastmasters Club</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19266,13 +19264,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L180" s="8" t="inlineStr">
         <is>
@@ -19293,7 +19291,7 @@
         </is>
       </c>
       <c r="P180" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q180" s="10" t="n">
         <v>0</v>
@@ -19302,13 +19300,13 @@
         <v>0</v>
       </c>
       <c r="S180" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T180" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V180" s="10" t="n">
         <v>0</v>
@@ -19317,7 +19315,7 @@
         <v>0</v>
       </c>
       <c r="X180" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y180" s="10" t="n">
         <v>0</v>
@@ -19329,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="AB180" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC180" s="4" t="inlineStr"/>
     </row>
@@ -19345,15 +19343,15 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>28676815</v>
+        <v>28679666</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Lome Synergie Toastmasters Club</t>
+          <t>Estrella TMC</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19367,13 +19365,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="L181" s="8" t="inlineStr">
         <is>
@@ -19394,7 +19392,7 @@
         </is>
       </c>
       <c r="P181" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q181" s="10" t="n">
         <v>0</v>
@@ -19405,20 +19403,20 @@
       <c r="S181" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V181" s="9" t="n">
-        <v>4</v>
+      <c r="T181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="W181" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X181" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y181" s="10" t="n">
         <v>0</v>
@@ -19430,13 +19428,9 @@
         <v>1</v>
       </c>
       <c r="AB181" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC181" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19450,15 +19444,15 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>28677845</v>
+        <v>28676815</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Ora Bilingual Toastmasters Club</t>
+          <t>Lome Synergie Toastmasters Club</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19472,13 +19466,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
       <c r="L182" s="8" t="inlineStr">
         <is>
@@ -19499,7 +19493,7 @@
         </is>
       </c>
       <c r="P182" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q182" s="10" t="n">
         <v>0</v>
@@ -19510,20 +19504,20 @@
       <c r="S182" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T182" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="10" t="n">
-        <v>0</v>
+      <c r="T182" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V182" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W182" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" s="10" t="n">
         <v>2</v>
+      </c>
+      <c r="X182" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Y182" s="10" t="n">
         <v>0</v>
@@ -19555,11 +19549,11 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>28676325</v>
+        <v>28677845</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Orabank Togo Toastmasters Club</t>
+          <t>Ora Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
@@ -19577,13 +19571,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="L183" s="8" t="inlineStr">
         <is>
@@ -19660,11 +19654,11 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>28675536</v>
+        <v>28676325</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>SHERIA TOASTMASTERS CLUB DE LOME</t>
+          <t>Orabank Togo Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
@@ -19682,13 +19676,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="L184" s="8" t="inlineStr">
         <is>
@@ -19732,8 +19726,8 @@
       <c r="W184" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="9" t="n">
-        <v>6</v>
+      <c r="X184" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="Y184" s="10" t="n">
         <v>0</v>
@@ -19745,9 +19739,13 @@
         <v>1</v>
       </c>
       <c r="AB184" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC184" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -19757,19 +19755,19 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>7440289</v>
+        <v>28675536</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Ahoefa Toastmasters Club De Lome</t>
+          <t>SHERIA TOASTMASTERS CLUB DE LOME</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19783,13 +19781,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
@@ -19810,7 +19808,7 @@
         </is>
       </c>
       <c r="P185" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q185" s="10" t="n">
         <v>0</v>
@@ -19818,17 +19816,17 @@
       <c r="R185" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S185" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T185" s="9" t="n">
-        <v>1</v>
+      <c r="S185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U185" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V185" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W185" s="10" t="n">
         <v>0</v>
@@ -19846,13 +19844,9 @@
         <v>1</v>
       </c>
       <c r="AB185" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC185" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -19866,15 +19860,15 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>7836464</v>
+        <v>7440289</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Emergence Toastmasters Club De Lome</t>
+          <t>Ahoefa Toastmasters Club De Lome</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19888,13 +19882,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="L186" s="8" t="inlineStr">
         <is>
@@ -19923,11 +19917,11 @@
       <c r="R186" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S186" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" s="10" t="n">
-        <v>0</v>
+      <c r="S186" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T186" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U186" s="10" t="n">
         <v>0</v>
@@ -19939,21 +19933,25 @@
         <v>0</v>
       </c>
       <c r="X186" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y186" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="10" t="n">
-        <v>0</v>
+      <c r="Z186" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA186" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC186" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19967,15 +19965,15 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>6619053</v>
+        <v>7836464</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Golden Toastmasters Club Bilingue De Lomé</t>
+          <t>Emergence Toastmasters Club De Lome</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19989,13 +19987,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L187" s="8" t="inlineStr">
         <is>
@@ -20019,7 +20017,7 @@
         <v>1</v>
       </c>
       <c r="Q187" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R187" s="10" t="n">
         <v>0</v>
@@ -20027,38 +20025,34 @@
       <c r="S187" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T187" s="9" t="n">
-        <v>1</v>
+      <c r="T187" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U187" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V187" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W187" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X187" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y187" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>1</v>
+      <c r="Z187" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA187" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC187" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -20072,11 +20066,11 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>28677254</v>
+        <v>6619053</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>GTA VIE</t>
+          <t>Golden Toastmasters Club Bilingue De Lomé</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
@@ -20094,13 +20088,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="L188" s="8" t="inlineStr">
         <is>
@@ -20121,10 +20115,10 @@
         </is>
       </c>
       <c r="P188" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q188" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R188" s="10" t="n">
         <v>0</v>
@@ -20132,20 +20126,20 @@
       <c r="S188" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T188" s="10" t="n">
-        <v>0</v>
+      <c r="T188" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U188" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V188" s="9" t="n">
-        <v>4</v>
+      <c r="V188" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="W188" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X188" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y188" s="10" t="n">
         <v>0</v>
@@ -20177,15 +20171,15 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>28680378</v>
+        <v>28677254</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Light Elite Bilingue de Lomé</t>
+          <t>GTA VIE</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -20199,17 +20193,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L189" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M189" s="7" t="n">
@@ -20226,7 +20220,7 @@
         </is>
       </c>
       <c r="P189" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q189" s="10" t="n">
         <v>0</v>
@@ -20237,8 +20231,8 @@
       <c r="S189" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T189" s="9" t="n">
-        <v>1</v>
+      <c r="T189" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U189" s="10" t="n">
         <v>0</v>
@@ -20247,7 +20241,7 @@
         <v>4</v>
       </c>
       <c r="W189" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X189" s="9" t="n">
         <v>6</v>
@@ -20262,31 +20256,35 @@
         <v>1</v>
       </c>
       <c r="AB189" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC189" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC189" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>28678435</v>
+        <v>28680378</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>CRS Guinée Toastmasters Club</t>
+          <t>Light Elite Bilingue de Lomé</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -20300,25 +20298,25 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L190" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M190" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N190" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O190" s="8" t="inlineStr">
@@ -20327,10 +20325,10 @@
         </is>
       </c>
       <c r="P190" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q190" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R190" s="10" t="n">
         <v>0</v>
@@ -20338,29 +20336,29 @@
       <c r="S190" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="10" t="n">
-        <v>0</v>
+      <c r="T190" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U190" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V190" s="10" t="n">
-        <v>0</v>
+      <c r="V190" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W190" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X190" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X190" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="Y190" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z190" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA190" s="10" t="n">
-        <v>0</v>
+      <c r="Z190" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA190" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AB190" s="4" t="n">
         <v>1</v>
@@ -20379,15 +20377,15 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>7995913</v>
+        <v>28678435</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Demosthene Toastmasters Club</t>
+          <t>CRS Guinée Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20401,25 +20399,25 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L191" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M191" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N191" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O191" s="8" t="inlineStr">
@@ -20439,38 +20437,34 @@
       <c r="S191" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T191" s="9" t="n">
-        <v>1</v>
+      <c r="T191" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U191" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V191" s="9" t="n">
-        <v>4</v>
+      <c r="V191" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="W191" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X191" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X191" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="Y191" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z191" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA191" s="9" t="n">
-        <v>1</v>
+      <c r="Z191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AB191" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC191" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -20484,15 +20478,15 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>28679516</v>
+        <v>7995913</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>IfD Toastmasters Club</t>
+          <t>Demosthene Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20506,13 +20500,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -20544,34 +20538,38 @@
       <c r="S192" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T192" s="10" t="n">
-        <v>0</v>
+      <c r="T192" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U192" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V192" s="10" t="n">
-        <v>1</v>
+      <c r="V192" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W192" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X192" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y192" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z192" s="10" t="n">
-        <v>0</v>
+      <c r="Z192" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA192" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB192" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC192" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC192" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -20585,15 +20583,15 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>7995924</v>
+        <v>28679516</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Medicus Toastmasters Club</t>
+          <t>IfD Toastmasters Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20607,17 +20605,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L193" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M193" s="7" t="n">
@@ -20634,16 +20632,16 @@
         </is>
       </c>
       <c r="P193" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q193" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R193" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S193" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T193" s="10" t="n">
         <v>0</v>
@@ -20651,32 +20649,28 @@
       <c r="U193" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V193" s="9" t="n">
+      <c r="V193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W193" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W193" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="Y193" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z193" s="9" t="n">
-        <v>1</v>
+      <c r="Z193" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA193" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB193" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC193" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -20690,11 +20684,11 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>3355879</v>
+        <v>7995924</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Nimba Toastmasters Club</t>
+          <t>Medicus Toastmasters Club</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
@@ -20712,17 +20706,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L194" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="7" t="n">
@@ -20742,13 +20736,13 @@
         <v>1</v>
       </c>
       <c r="Q194" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S194" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T194" s="10" t="n">
         <v>0</v>
@@ -20760,10 +20754,10 @@
         <v>4</v>
       </c>
       <c r="W194" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X194" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y194" s="10" t="n">
         <v>0</v>
@@ -20791,19 +20785,19 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>5495364</v>
+        <v>3355879</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Academie</t>
+          <t>Nimba Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20817,17 +20811,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L195" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M195" s="7" t="n">
@@ -20844,7 +20838,7 @@
         </is>
       </c>
       <c r="P195" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" s="10" t="n">
         <v>0</v>
@@ -20861,11 +20855,11 @@
       <c r="U195" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="10" t="n">
-        <v>3</v>
+      <c r="V195" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W195" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X195" s="9" t="n">
         <v>6</v>
@@ -20900,15 +20894,15 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>28680031</v>
+        <v>5495364</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Ciceron Online</t>
+          <t>Academie</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20922,13 +20916,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
@@ -20949,7 +20943,7 @@
         </is>
       </c>
       <c r="P196" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q196" s="10" t="n">
         <v>0</v>
@@ -20966,11 +20960,11 @@
       <c r="U196" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V196" s="9" t="n">
-        <v>4</v>
+      <c r="V196" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="W196" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X196" s="9" t="n">
         <v>6</v>
@@ -20985,9 +20979,13 @@
         <v>1</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC196" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC196" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -21001,15 +20999,15 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>28676188</v>
+        <v>28680031</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Tenin Legacy Toastmasters Club</t>
+          <t>Ciceron Online</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -21023,10 +21021,10 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K197" s="4" t="n">
         <v>-13</v>
@@ -21061,8 +21059,8 @@
       <c r="S197" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T197" s="10" t="n">
-        <v>0</v>
+      <c r="T197" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U197" s="10" t="n">
         <v>0</v>
@@ -21071,10 +21069,10 @@
         <v>4</v>
       </c>
       <c r="W197" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X197" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y197" s="10" t="n">
         <v>0</v>
@@ -21086,13 +21084,9 @@
         <v>1</v>
       </c>
       <c r="AB197" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC197" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -21106,15 +21100,15 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>7711825</v>
+        <v>28676188</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>UN &amp; Partners Toastmasters Club</t>
+          <t>Tenin Legacy Toastmasters Club</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -21128,17 +21122,17 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L198" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M198" s="7" t="n">
@@ -21158,7 +21152,7 @@
         <v>1</v>
       </c>
       <c r="Q198" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R198" s="10" t="n">
         <v>0</v>
@@ -21166,8 +21160,8 @@
       <c r="S198" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T198" s="9" t="n">
-        <v>1</v>
+      <c r="T198" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U198" s="10" t="n">
         <v>0</v>
@@ -21175,11 +21169,11 @@
       <c r="V198" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W198" s="9" t="n">
-        <v>12</v>
+      <c r="W198" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="X198" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y198" s="10" t="n">
         <v>0</v>
@@ -21207,19 +21201,19 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>7831186</v>
+        <v>7711825</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>ELLES Toastmasters Club</t>
+          <t>UN &amp; Partners Toastmasters Club</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -21233,17 +21227,17 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="J199" s="4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L199" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M199" s="7" t="n">
@@ -21263,7 +21257,7 @@
         <v>1</v>
       </c>
       <c r="Q199" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" s="10" t="n">
         <v>0</v>
@@ -21280,11 +21274,11 @@
       <c r="V199" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W199" s="10" t="n">
-        <v>1</v>
+      <c r="W199" s="9" t="n">
+        <v>13</v>
       </c>
       <c r="X199" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y199" s="10" t="n">
         <v>0</v>
@@ -21296,11 +21290,11 @@
         <v>1</v>
       </c>
       <c r="AB199" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC199" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -21316,15 +21310,15 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>28679218</v>
+        <v>7831186</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Kakande Toastmasters Club</t>
+          <t>ELLES Toastmasters Club</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -21338,17 +21332,17 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J200" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J200" s="4" t="n">
-        <v>35</v>
-      </c>
       <c r="K200" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L200" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="7" t="n">
@@ -21365,7 +21359,7 @@
         </is>
       </c>
       <c r="P200" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q200" s="10" t="n">
         <v>0</v>
@@ -21376,20 +21370,20 @@
       <c r="S200" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T200" s="10" t="n">
-        <v>0</v>
+      <c r="T200" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U200" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V200" s="10" t="n">
-        <v>3</v>
+      <c r="V200" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W200" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X200" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y200" s="10" t="n">
         <v>0</v>
@@ -21421,15 +21415,15 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>7774752</v>
+        <v>28679218</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Panache Toastmaster Club</t>
+          <t>Kakande Toastmasters Club</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21443,17 +21437,17 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J201" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L201" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-15</v>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M201" s="7" t="n">
@@ -21470,7 +21464,7 @@
         </is>
       </c>
       <c r="P201" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q201" s="10" t="n">
         <v>0</v>
@@ -21481,20 +21475,20 @@
       <c r="S201" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U201" s="9" t="n">
-        <v>1</v>
+      <c r="T201" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="V201" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W201" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X201" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y201" s="10" t="n">
         <v>0</v>
@@ -21506,11 +21500,11 @@
         <v>1</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC201" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -21526,15 +21520,15 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>28677469</v>
+        <v>7774752</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>UN &amp; Partners On The Field</t>
+          <t>Panache Toastmaster Club</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -21548,13 +21542,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
@@ -21586,34 +21580,38 @@
       <c r="S202" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T202" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" s="10" t="n">
-        <v>0</v>
+      <c r="T202" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U202" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V202" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W202" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X202" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y202" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z202" s="10" t="n">
-        <v>0</v>
+      <c r="Z202" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA202" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC202" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -21623,19 +21621,19 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>7839004</v>
+        <v>28677469</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>ESPERANCE Toastmasters Club</t>
+          <t>UN &amp; Partners On The Field</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21649,13 +21647,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="L203" s="8" t="inlineStr">
         <is>
@@ -21676,7 +21674,7 @@
         </is>
       </c>
       <c r="P203" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q203" s="10" t="n">
         <v>0</v>
@@ -21694,31 +21692,27 @@
         <v>0</v>
       </c>
       <c r="V203" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W203" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X203" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y203" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z203" s="9" t="n">
-        <v>1</v>
+      <c r="Z203" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA203" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC203" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -21732,11 +21726,11 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>28676381</v>
+        <v>7839004</v>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>K-CONCEPT Toastmasters Club</t>
+          <t>ESPERANCE Toastmasters Club</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
@@ -21757,10 +21751,10 @@
         <v>8</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="L204" s="8" t="inlineStr">
         <is>
@@ -21781,7 +21775,7 @@
         </is>
       </c>
       <c r="P204" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q204" s="10" t="n">
         <v>0</v>
@@ -21790,7 +21784,7 @@
         <v>0</v>
       </c>
       <c r="S204" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T204" s="10" t="n">
         <v>0</v>
@@ -21799,7 +21793,7 @@
         <v>0</v>
       </c>
       <c r="V204" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W204" s="10" t="n">
         <v>0</v>
@@ -21817,11 +21811,11 @@
         <v>1</v>
       </c>
       <c r="AB204" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC204" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -21837,15 +21831,15 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>7852040</v>
+        <v>28676381</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Premium Toastmasters Club</t>
+          <t>K-CONCEPT Toastmasters Club</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21859,13 +21853,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J205" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L205" s="8" t="inlineStr">
         <is>
@@ -21886,31 +21880,31 @@
         </is>
       </c>
       <c r="P205" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q205" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R205" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S205" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T205" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T205" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U205" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="9" t="n">
-        <v>4</v>
+      <c r="V205" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="W205" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X205" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y205" s="10" t="n">
         <v>0</v>
@@ -21922,11 +21916,11 @@
         <v>1</v>
       </c>
       <c r="AB205" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC205" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -21942,15 +21936,15 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>28680405</v>
+        <v>7852040</v>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Tdh Guinée</t>
+          <t>Premium Toastmasters Club</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F206" s="6" t="n">
         <v>10</v>
@@ -21964,17 +21958,17 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J206" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L206" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M206" s="7" t="n">
@@ -21991,10 +21985,10 @@
         </is>
       </c>
       <c r="P206" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q206" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R206" s="10" t="n">
         <v>0</v>
@@ -22002,32 +21996,38 @@
       <c r="S206" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T206" s="10" t="n">
-        <v>0</v>
+      <c r="T206" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U206" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V206" s="10" t="n">
-        <v>0</v>
+      <c r="V206" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W206" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X206" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y206" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z206" s="10" t="n">
-        <v>0</v>
+      <c r="Z206" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA206" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB206" s="4" t="n"/>
-      <c r="AC206" s="4" t="inlineStr"/>
+      <c r="AB206" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC206" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -22041,15 +22041,15 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>4553130</v>
+        <v>28680405</v>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Tinkisso Prestige</t>
+          <t>Tdh Guinée</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F207" s="6" t="n">
         <v>10</v>
@@ -22063,13 +22063,13 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J207" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>0</v>
       </c>
       <c r="S207" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T207" s="10" t="n">
         <v>0</v>
@@ -22107,32 +22107,26 @@
       <c r="U207" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V207" s="9" t="n">
+      <c r="V207" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W207" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W207" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X207" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="Y207" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z207" s="9" t="n">
-        <v>1</v>
+      <c r="Z207" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA207" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB207" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC207" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB207" s="4" t="n"/>
+      <c r="AC207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -22142,19 +22136,19 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>28679700</v>
+        <v>4553130</v>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Kakilambe Toastmasters Club</t>
+          <t>Tinkisso Prestige</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F208" s="6" t="n">
         <v>10</v>
@@ -22168,13 +22162,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -22204,7 +22198,7 @@
         <v>0</v>
       </c>
       <c r="S208" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T208" s="10" t="n">
         <v>0</v>
@@ -22212,14 +22206,14 @@
       <c r="U208" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V208" s="10" t="n">
-        <v>2</v>
+      <c r="V208" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W208" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X208" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y208" s="10" t="n">
         <v>0</v>
@@ -22231,9 +22225,13 @@
         <v>1</v>
       </c>
       <c r="AB208" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC208" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC208" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -22247,15 +22245,15 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>28677497</v>
+        <v>28679700</v>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>OMS GUINEE Toastmasters Club</t>
+          <t>Kakilambe Toastmasters Club</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>10</v>
@@ -22269,17 +22267,17 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J209" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L209" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M209" s="7" t="n">
@@ -22296,10 +22294,10 @@
         </is>
       </c>
       <c r="P209" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q209" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R209" s="10" t="n">
         <v>0</v>
@@ -22314,31 +22312,27 @@
         <v>0</v>
       </c>
       <c r="V209" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W209" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X209" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y209" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z209" s="10" t="n">
-        <v>0</v>
+      <c r="Z209" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA209" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB209" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC209" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -22352,15 +22346,15 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>28678058</v>
+        <v>28677497</v>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Precious Line Women Leaders 10</t>
+          <t>OMS GUINEE Toastmasters Club</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>10</v>
@@ -22374,13 +22368,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="L210" s="8" t="inlineStr">
         <is>
@@ -22419,27 +22413,31 @@
         <v>0</v>
       </c>
       <c r="V210" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W210" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X210" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y210" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z210" s="9" t="n">
-        <v>1</v>
+      <c r="Z210" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA210" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC210" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC210" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -22453,11 +22451,11 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>28678593</v>
+        <v>28678058</v>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Women Leader Conakry</t>
+          <t>Precious Line Women Leaders 10</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
@@ -22475,13 +22473,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J211" s="4" t="n">
-        <v>21</v>
-      </c>
       <c r="K211" s="4" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="L211" s="8" t="inlineStr">
         <is>
@@ -22538,35 +22536,31 @@
         <v>1</v>
       </c>
       <c r="AB211" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC211" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>28679734</v>
+        <v>28678593</v>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>ASPRH Toastmasters Club</t>
+          <t>Women Leader Conakry</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>10</v>
@@ -22580,17 +22574,17 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L212" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L212" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M212" s="7" t="n">
@@ -22607,31 +22601,31 @@
         </is>
       </c>
       <c r="P212" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q212" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R212" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S212" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T212" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T212" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U212" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V212" s="9" t="n">
-        <v>4</v>
+      <c r="V212" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="W212" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X212" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y212" s="10" t="n">
         <v>0</v>
@@ -22643,9 +22637,13 @@
         <v>1</v>
       </c>
       <c r="AB212" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC212" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC212" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -22659,15 +22657,15 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>1266972</v>
+        <v>28679734</v>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Dakar Xewel Toastmasters Club</t>
+          <t>ASPRH Toastmasters Club</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>10</v>
@@ -22681,13 +22679,13 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J213" s="4" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
@@ -22707,32 +22705,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P213" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q213" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R213" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S213" s="9" t="n">
-        <v>2</v>
+      <c r="P213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R213" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="T213" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U213" s="9" t="n">
-        <v>1</v>
+      <c r="U213" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="V213" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W213" s="9" t="n">
-        <v>5</v>
+      <c r="W213" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="X213" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y213" s="10" t="n">
         <v>0</v>
@@ -22744,13 +22742,9 @@
         <v>1</v>
       </c>
       <c r="AB213" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC213" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -22764,15 +22758,15 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>4327499</v>
+        <v>1266972</v>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Gambia Elite Toastmasters</t>
+          <t>Dakar Xewel Toastmasters Club</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F214" s="6" t="n">
         <v>10</v>
@@ -22786,13 +22780,13 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J214" s="4" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
@@ -22812,32 +22806,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P214" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q214" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R214" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T214" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U214" s="10" t="n">
-        <v>0</v>
+      <c r="P214" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q214" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R214" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S214" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T214" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U214" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V214" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W214" s="10" t="n">
-        <v>3</v>
+      <c r="W214" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="X214" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y214" s="10" t="n">
         <v>0</v>
@@ -22869,15 +22863,15 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>28675411</v>
+        <v>4327499</v>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Sonatel Club Alpha</t>
+          <t>Gambia Elite Toastmasters</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -22891,17 +22885,17 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J215" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L215" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M215" s="7" t="n">
@@ -22918,7 +22912,7 @@
         </is>
       </c>
       <c r="P215" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q215" s="10" t="n">
         <v>0</v>
@@ -22927,7 +22921,7 @@
         <v>0</v>
       </c>
       <c r="S215" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T215" s="10" t="n">
         <v>0</v>
@@ -22938,8 +22932,8 @@
       <c r="V215" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W215" s="9" t="n">
-        <v>8</v>
+      <c r="W215" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="X215" s="9" t="n">
         <v>6</v>
@@ -22954,9 +22948,13 @@
         <v>1</v>
       </c>
       <c r="AB215" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC215" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC215" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -22966,19 +22964,19 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>28679870</v>
+        <v>28675411</v>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>BIO 24</t>
+          <t>Sonatel Club Alpha</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>10</v>
@@ -22992,17 +22990,17 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J216" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L216" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M216" s="7" t="n">
@@ -23036,11 +23034,11 @@
       <c r="U216" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V216" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W216" s="10" t="n">
-        <v>0</v>
+      <c r="V216" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W216" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="X216" s="9" t="n">
         <v>6</v>
@@ -23048,14 +23046,14 @@
       <c r="Y216" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z216" s="10" t="n">
-        <v>0</v>
+      <c r="Z216" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA216" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB216" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC216" s="4" t="inlineStr"/>
     </row>
@@ -23071,15 +23069,15 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>7753552</v>
+        <v>28679870</v>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Dakar Kallaama Toastmasters Club</t>
+          <t>BIO 24</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217" s="6" t="n">
         <v>10</v>
@@ -23093,13 +23091,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>-8</v>
+        <v>-21</v>
       </c>
       <c r="L217" s="8" t="inlineStr">
         <is>
@@ -23120,10 +23118,10 @@
         </is>
       </c>
       <c r="P217" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q217" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R217" s="10" t="n">
         <v>0</v>
@@ -23144,25 +23142,21 @@
         <v>0</v>
       </c>
       <c r="X217" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y217" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z217" s="9" t="n">
-        <v>1</v>
+      <c r="Z217" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="AA217" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB217" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC217" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -23176,15 +23170,15 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>6800139</v>
+        <v>7753552</v>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Dakar Teranga Toastmasters Club</t>
+          <t>Dakar Kallaama Toastmasters Club</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F218" s="6" t="n">
         <v>10</v>
@@ -23198,17 +23192,17 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J218" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L218" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L218" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M218" s="7" t="n">
@@ -23224,29 +23218,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P218" s="9" t="n">
-        <v>4</v>
+      <c r="P218" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="Q218" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R218" s="9" t="n">
+      <c r="R218" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V218" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S218" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T218" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U218" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V218" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W218" s="9" t="n">
-        <v>9</v>
+      <c r="W218" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="X218" s="9" t="n">
         <v>7</v>
@@ -23261,11 +23255,11 @@
         <v>1</v>
       </c>
       <c r="AB218" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC218" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -23281,35 +23275,35 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>7835571</v>
+        <v>6800139</v>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>DTA Toastmasters Club</t>
+          <t>Dakar Teranga Toastmasters Club</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F219" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G219" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="J219" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K219" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="F219" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G219" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H219" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I219" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="J219" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="K219" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
@@ -23335,11 +23329,11 @@
       <c r="Q219" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" s="10" t="n">
-        <v>0</v>
+      <c r="R219" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S219" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T219" s="9" t="n">
         <v>1</v>
@@ -23351,7 +23345,7 @@
         <v>4</v>
       </c>
       <c r="W219" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X219" s="9" t="n">
         <v>7</v>
@@ -23386,15 +23380,15 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>28680055</v>
+        <v>7835571</v>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Nasso Speakers</t>
+          <t>DTA Toastmasters Club</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>10</v>
@@ -23408,17 +23402,17 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="J220" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L220" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M220" s="7" t="n">
@@ -23434,32 +23428,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" s="10" t="n">
-        <v>0</v>
+      <c r="P220" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q220" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V220" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W220" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S220" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T220" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U220" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V220" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W220" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="X220" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y220" s="10" t="n">
         <v>0</v>
@@ -23471,9 +23465,13 @@
         <v>1</v>
       </c>
       <c r="AB220" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC220" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC220" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -23483,19 +23481,19 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>28678737</v>
+        <v>28680055</v>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Baraka TMC</t>
+          <t>Nasso Speakers</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>10</v>
@@ -23509,17 +23507,17 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J221" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K221" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L221" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L221" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M221" s="7" t="n">
@@ -23536,10 +23534,10 @@
         </is>
       </c>
       <c r="P221" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q221" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R221" s="10" t="n">
         <v>0</v>
@@ -23547,20 +23545,20 @@
       <c r="S221" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T221" s="9" t="n">
-        <v>1</v>
+      <c r="T221" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U221" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V221" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W221" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X221" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y221" s="10" t="n">
         <v>0</v>
@@ -23572,13 +23570,9 @@
         <v>1</v>
       </c>
       <c r="AB221" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC221" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -23592,15 +23586,15 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>7050414</v>
+        <v>28678737</v>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Dakar Jambaar Toastmasters Club</t>
+          <t>Baraka TMC</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F222" s="6" t="n">
         <v>10</v>
@@ -23614,13 +23608,13 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
@@ -23640,29 +23634,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P222" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q222" s="9" t="n">
+      <c r="P222" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R222" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S222" s="9" t="n">
+      <c r="Q222" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R222" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U222" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T222" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U222" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W222" s="9" t="n">
-        <v>6</v>
+      <c r="W222" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="X222" s="9" t="n">
         <v>7</v>
@@ -23697,15 +23691,15 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>28680049</v>
+        <v>7050414</v>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Maxamayni Toastmasters Club</t>
+          <t>Dakar Jambaar Toastmasters Club</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>10</v>
@@ -23719,13 +23713,13 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J223" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K223" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
@@ -23745,17 +23739,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P223" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q223" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S223" s="10" t="n">
-        <v>0</v>
+      <c r="P223" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q223" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R223" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S223" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T223" s="9" t="n">
         <v>1</v>
@@ -23763,11 +23757,11 @@
       <c r="U223" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V223" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W223" s="10" t="n">
-        <v>0</v>
+      <c r="V223" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W223" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="X223" s="9" t="n">
         <v>7</v>
@@ -23782,9 +23776,13 @@
         <v>1</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC223" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC223" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -23798,15 +23796,15 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>28678158</v>
+        <v>28680049</v>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Port Autonome de Dakar TM Club</t>
+          <t>Maxamayni Toastmasters Club</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F224" s="6" t="n">
         <v>10</v>
@@ -23820,17 +23818,17 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J224" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L224" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M224" s="7" t="n">
@@ -23858,8 +23856,8 @@
       <c r="S224" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T224" s="10" t="n">
-        <v>0</v>
+      <c r="T224" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U224" s="10" t="n">
         <v>0</v>
@@ -23871,25 +23869,21 @@
         <v>0</v>
       </c>
       <c r="X224" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y224" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z224" s="10" t="n">
-        <v>0</v>
+      <c r="Z224" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA224" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC224" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -23903,15 +23897,15 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>28676581</v>
+        <v>28678158</v>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Women Leaders Dakar TMC</t>
+          <t>Port Autonome de Dakar TM Club</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>10</v>
@@ -23925,17 +23919,17 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J225" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L225" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L225" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M225" s="7" t="n">
@@ -23952,7 +23946,7 @@
         </is>
       </c>
       <c r="P225" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q225" s="10" t="n">
         <v>0</v>
@@ -23960,39 +23954,39 @@
       <c r="R225" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S225" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T225" s="9" t="n">
-        <v>1</v>
+      <c r="S225" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U225" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V225" s="9" t="n">
-        <v>4</v>
+      <c r="V225" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="W225" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X225" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y225" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z225" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA225" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB225" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y225" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z225" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA225" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB225" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="AC225" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -24004,19 +23998,19 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>28676462</v>
+        <v>28676581</v>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Bideew Toastmasters Club</t>
+          <t>Women Leaders Dakar TMC</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F226" s="6" t="n">
         <v>10</v>
@@ -24030,13 +24024,13 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J226" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
@@ -24056,20 +24050,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P226" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q226" s="9" t="n">
+      <c r="P226" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R226" s="9" t="n">
-        <v>2</v>
+      <c r="Q226" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="S226" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T226" s="10" t="n">
-        <v>0</v>
+      <c r="T226" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U226" s="10" t="n">
         <v>0</v>
@@ -24078,7 +24072,7 @@
         <v>4</v>
       </c>
       <c r="W226" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X226" s="9" t="n">
         <v>7</v>
@@ -24113,15 +24107,15 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>7978248</v>
+        <v>28676462</v>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Ndayane Toastmasters Club</t>
+          <t>Bideew Toastmasters Club</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F227" s="6" t="n">
         <v>10</v>
@@ -24135,17 +24129,17 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J227" s="4" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L227" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L227" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M227" s="7" t="n">
@@ -24161,20 +24155,20 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T227" s="9" t="n">
-        <v>1</v>
+      <c r="P227" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q227" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R227" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S227" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T227" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="U227" s="10" t="n">
         <v>0</v>
@@ -24198,9 +24192,13 @@
         <v>1</v>
       </c>
       <c r="AB227" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC227" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC227" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -24214,15 +24212,15 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>28679717</v>
+        <v>7978248</v>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>New Life</t>
+          <t>Ndayane Toastmasters Club</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F228" s="6" t="n">
         <v>10</v>
@@ -24236,13 +24234,13 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J228" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K228" s="4" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="L228" s="8" t="inlineStr">
         <is>
@@ -24263,7 +24261,7 @@
         </is>
       </c>
       <c r="P228" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q228" s="10" t="n">
         <v>0</v>
@@ -24274,17 +24272,17 @@
       <c r="S228" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T228" s="10" t="n">
-        <v>0</v>
+      <c r="T228" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U228" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V228" s="10" t="n">
-        <v>0</v>
+      <c r="V228" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W228" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X228" s="9" t="n">
         <v>7</v>
@@ -24299,7 +24297,7 @@
         <v>1</v>
       </c>
       <c r="AB228" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC228" s="4" t="inlineStr"/>
     </row>
@@ -24315,11 +24313,11 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>28676307</v>
+        <v>28679717</v>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Sahara Toastmasters Club</t>
+          <t>New Life</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
@@ -24337,13 +24335,13 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J229" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="L229" s="8" t="inlineStr">
         <is>
@@ -24367,13 +24365,13 @@
         <v>2</v>
       </c>
       <c r="Q229" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S229" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T229" s="10" t="n">
         <v>0</v>
@@ -24400,13 +24398,9 @@
         <v>1</v>
       </c>
       <c r="AB229" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC229" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -24420,15 +24414,15 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>28676948</v>
+        <v>28676307</v>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Yassir Senegal</t>
+          <t>Sahara Toastmasters Club</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>10</v>
@@ -24442,13 +24436,13 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J230" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K230" s="4" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="L230" s="8" t="inlineStr">
         <is>
@@ -24469,16 +24463,16 @@
         </is>
       </c>
       <c r="P230" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q230" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R230" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S230" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T230" s="10" t="n">
         <v>0</v>
@@ -24493,24 +24487,129 @@
         <v>0</v>
       </c>
       <c r="X230" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA230" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB230" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC230" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v>28676948</v>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>Yassir Senegal</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G231" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J231" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K231" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L231" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M231" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N231" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O231" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="Y230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA230" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB230" s="4" t="n">
+      <c r="Y231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB231" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AC230" s="4" t="inlineStr"/>
+      <c r="AC231" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC230"/>
+  <autoFilter ref="A1:AC231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24521,7 +24620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -24630,7 +24729,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -24645,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -24663,7 +24762,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -24795,7 +24894,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -24828,7 +24927,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -24861,7 +24960,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -24894,7 +24993,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -24927,7 +25026,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -24960,7 +25059,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -25059,7 +25158,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -25092,7 +25191,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -25125,7 +25224,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -25158,7 +25257,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -25257,13 +25356,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -25316,29 +25415,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -25349,20 +25448,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -25371,7 +25470,7 @@
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -25382,29 +25481,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -25415,14 +25514,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -25434,43 +25533,43 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -25481,14 +25580,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -25500,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -25514,20 +25613,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -25547,20 +25646,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -25580,20 +25679,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -25608,25 +25707,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25635,7 +25734,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -25646,20 +25745,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -25679,20 +25778,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25701,7 +25800,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -25712,20 +25811,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25734,7 +25833,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25745,14 +25844,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -25767,25 +25866,25 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -25797,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -25811,29 +25910,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -25844,14 +25943,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -25877,20 +25976,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -25899,7 +25998,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -25910,20 +26009,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25932,40 +26031,40 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.75</v>
+        <v>4.25</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>4</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -25976,17 +26075,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="n">
-        <v>4.25</v>
-      </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -25998,7 +26097,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -26009,20 +26108,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -26031,7 +26130,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -26042,14 +26141,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -26064,44 +26163,11 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:I46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/94/inyear.xlsx
+++ b/docs/d/94/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>4</v>
       </c>
       <c r="Q2" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="10" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>0</v>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="Q32" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0</v>
@@ -4001,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W32" s="10" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="P34" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>0</v>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>1</v>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5965,8 +5965,8 @@
       <c r="S51" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="T51" s="10" t="n">
-        <v>0</v>
+      <c r="T51" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="10" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="R57" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="10" t="n">
         <v>0</v>
@@ -8403,13 +8403,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>2</v>
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="10" t="n">
         <v>0</v>
@@ -9782,7 +9782,7 @@
         <v>1</v>
       </c>
       <c r="Q88" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="10" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9892,14 +9892,14 @@
       <c r="R89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="S89" s="10" t="n">
-        <v>1</v>
+      <c r="S89" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T89" s="9" t="n">
         <v>1</v>
       </c>
       <c r="U89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>4</v>
@@ -10483,13 +10483,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>7</v>
@@ -12380,7 +12380,7 @@
         </is>
       </c>
       <c r="P113" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q113" s="10" t="n">
         <v>1</v>
@@ -12694,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T116" s="9" t="n">
         <v>1</v>
@@ -12864,13 +12864,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X118" s="9" t="n">
         <v>7</v>
@@ -13276,13 +13276,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -13678,13 +13678,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X126" s="9" t="n">
         <v>4</v>
@@ -13918,7 +13918,7 @@
         <v>2</v>
       </c>
       <c r="Q128" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="10" t="n">
         <v>0</v>
@@ -14090,13 +14090,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -14733,16 +14733,16 @@
         </is>
       </c>
       <c r="P136" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S136" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" s="10" t="n">
         <v>0</v>
@@ -15423,13 +15423,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X143" s="9" t="n">
         <v>7</v>
@@ -15930,7 +15930,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q148" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="10" t="n">
         <v>0</v>
@@ -15982,8 +15982,8 @@
       <c r="S148" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T148" s="10" t="n">
-        <v>0</v>
+      <c r="T148" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U148" s="10" t="n">
         <v>0</v>
@@ -16076,7 +16076,7 @@
         </is>
       </c>
       <c r="P149" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q149" s="10" t="n">
         <v>0</v>
@@ -16496,7 +16496,7 @@
         </is>
       </c>
       <c r="P153" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="10" t="n">
         <v>0</v>
@@ -16570,13 +16570,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X154" s="9" t="n">
         <v>7</v>
@@ -17091,13 +17091,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -17124,10 +17124,10 @@
         <v>2</v>
       </c>
       <c r="R159" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S159" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" s="9" t="n">
         <v>1</v>
@@ -17196,17 +17196,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L160" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -18127,13 +18127,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18794,8 +18794,8 @@
       <c r="T175" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U175" s="10" t="n">
-        <v>0</v>
+      <c r="U175" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V175" s="9" t="n">
         <v>4</v>
@@ -19060,13 +19060,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q178" s="9" t="n">
         <v>2</v>
@@ -19108,7 +19108,7 @@
         <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X178" s="9" t="n">
         <v>7</v>
@@ -19306,7 +19306,7 @@
         <v>1</v>
       </c>
       <c r="U180" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V180" s="10" t="n">
         <v>0</v>
@@ -20916,13 +20916,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
@@ -21021,13 +21021,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>4</v>
       </c>
       <c r="W197" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X197" s="9" t="n">
         <v>6</v>
@@ -22294,7 +22294,7 @@
         </is>
       </c>
       <c r="P209" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q209" s="10" t="n">
         <v>1</v>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -22885,13 +22885,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22932,8 +22932,8 @@
       <c r="V215" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W215" s="10" t="n">
-        <v>3</v>
+      <c r="W215" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="X215" s="9" t="n">
         <v>6</v>
@@ -22990,13 +22990,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="E220" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>10</v>
@@ -23402,13 +23402,13 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
@@ -23434,8 +23434,8 @@
       <c r="Q220" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R220" s="10" t="n">
-        <v>1</v>
+      <c r="R220" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S220" s="9" t="n">
         <v>2</v>
@@ -23450,7 +23450,7 @@
         <v>4</v>
       </c>
       <c r="W220" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X220" s="9" t="n">
         <v>7</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F222" s="6" t="n">
         <v>10</v>
@@ -23608,13 +23608,13 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
@@ -23652,11 +23652,11 @@
       <c r="U222" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V222" s="10" t="n">
-        <v>2</v>
+      <c r="V222" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W222" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X222" s="9" t="n">
         <v>7</v>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>10</v>
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K223" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
@@ -23754,14 +23754,14 @@
       <c r="T223" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U223" s="10" t="n">
-        <v>0</v>
+      <c r="U223" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V223" s="9" t="n">
         <v>4</v>
       </c>
       <c r="W223" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X223" s="9" t="n">
         <v>7</v>
@@ -23905,7 +23905,7 @@
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>10</v>
@@ -23919,13 +23919,13 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
       <c r="L225" s="8" t="inlineStr">
         <is>
@@ -23963,11 +23963,11 @@
       <c r="U225" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V225" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W225" s="10" t="n">
-        <v>0</v>
+      <c r="V225" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W225" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="X225" s="9" t="n">
         <v>6</v>
@@ -24129,13 +24129,13 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         </is>
       </c>
       <c r="P227" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q227" s="9" t="n">
         <v>2</v>
@@ -24177,7 +24177,7 @@
         <v>4</v>
       </c>
       <c r="W227" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X227" s="9" t="n">
         <v>7</v>
@@ -24264,7 +24264,7 @@
         <v>0</v>
       </c>
       <c r="Q228" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R228" s="10" t="n">
         <v>0</v>
@@ -24422,7 +24422,7 @@
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>10</v>
@@ -24436,17 +24436,17 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K230" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L230" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L230" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M230" s="7" t="n">
@@ -24480,8 +24480,8 @@
       <c r="U230" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V230" s="10" t="n">
-        <v>0</v>
+      <c r="V230" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W230" s="10" t="n">
         <v>0</v>
@@ -24577,7 +24577,7 @@
         <v>0</v>
       </c>
       <c r="S231" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T231" s="10" t="n">
         <v>0</v>
@@ -24960,7 +24960,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -25224,7 +25224,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -25587,13 +25587,13 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -25701,7 +25701,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -25785,7 +25785,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -26049,7 +26049,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -26082,7 +26082,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -26115,7 +26115,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -26148,7 +26148,7 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -26163,7 +26163,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
